--- a/apps/admin/public/textbook_template.xlsx
+++ b/apps/admin/public/textbook_template.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adki8\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adki8\Desktop\kusano-system\apps\admin\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E16A5E55-2F59-4C9B-8931-A8D2E5AEBC72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94616924-31B7-4BF4-8258-C3A04DB0B890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{16DF0547-09A0-4A85-8F6A-FE028C921A08}"/>
+    <workbookView xWindow="3510" yWindow="1290" windowWidth="24720" windowHeight="14190" xr2:uid="{16DF0547-09A0-4A85-8F6A-FE028C921A08}"/>
   </bookViews>
   <sheets>
     <sheet name="原紙" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">原紙!$B$1:$K$41</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">原紙!$B$1:$K$39</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="37">
   <si>
     <t>くさの書店　外商部　採用注文書</t>
     <rPh sb="3" eb="5">
@@ -414,29 +414,6 @@
   </si>
   <si>
     <t>グレード</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>きんぶん図書</t>
-    <rPh sb="4" eb="6">
-      <t>トショ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>長崎県教科書株式会社</t>
-    <rPh sb="0" eb="2">
-      <t>ナガサキ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ケン</t>
-    </rPh>
-    <rPh sb="3" eb="6">
-      <t>キョウカショ</t>
-    </rPh>
-    <rPh sb="6" eb="10">
-      <t>カブシキガイシャ</t>
-    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -804,7 +781,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -858,9 +835,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -873,7 +847,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -936,39 +913,6 @@
     <xf numFmtId="6" fontId="8" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -993,10 +937,34 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="6" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="6" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1304,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92F2D319-5469-4119-B8C1-84261C504772}">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="16.85546875" customWidth="1"/>
@@ -1330,49 +1298,47 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
     </row>
-    <row r="2" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1"/>
-      <c r="B2" s="45" t="s">
-        <v>37</v>
-      </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="47" t="s">
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2" s="54"/>
       <c r="L2" s="1"/>
     </row>
-    <row r="3" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1"/>
-      <c r="B3" s="45" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="H3" s="49"/>
-      <c r="I3" s="49"/>
-      <c r="J3" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="K3" s="50"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
       <c r="L3" s="1"/>
     </row>
     <row r="4" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="1"/>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="1"/>
+      <c r="B4" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
@@ -1380,50 +1346,52 @@
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
     </row>
-    <row r="5" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
-      <c r="B5" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
+      <c r="B5" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
+      <c r="K5" s="25"/>
       <c r="L5" s="1"/>
     </row>
-    <row r="6" spans="1:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
-      <c r="B6" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="25"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
+      <c r="B6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="38"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="38"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="40" t="s">
+        <v>6</v>
+      </c>
+      <c r="I6" s="40"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
       <c r="L6" s="1"/>
     </row>
     <row r="7" spans="1:12" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
-      <c r="B7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="38"/>
-      <c r="D7" s="38"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="39"/>
+      <c r="B7" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="47"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="49"/>
       <c r="H7" s="40" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I7" s="40"/>
       <c r="J7" s="38"/>
@@ -1432,16 +1400,14 @@
     </row>
     <row r="8" spans="1:12" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
-      <c r="B8" s="56" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="58"/>
-      <c r="D8" s="59"/>
-      <c r="E8" s="59"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="60"/>
+      <c r="B8" s="46"/>
+      <c r="C8" s="50"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="52"/>
       <c r="H8" s="40" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I8" s="40"/>
       <c r="J8" s="38"/>
@@ -1450,14 +1416,18 @@
     </row>
     <row r="9" spans="1:12" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
-      <c r="B9" s="57"/>
-      <c r="C9" s="61"/>
-      <c r="D9" s="62"/>
-      <c r="E9" s="62"/>
-      <c r="F9" s="62"/>
-      <c r="G9" s="63"/>
-      <c r="H9" s="40" t="s">
-        <v>9</v>
+      <c r="B9" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="43"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="41" t="s">
+        <v>12</v>
       </c>
       <c r="I9" s="40"/>
       <c r="J9" s="38"/>
@@ -1466,77 +1436,75 @@
     </row>
     <row r="10" spans="1:12" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
-      <c r="B10" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F10" s="43"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="41" t="s">
-        <v>12</v>
+      <c r="B10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="59"/>
+      <c r="D10" s="60"/>
+      <c r="E10" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="59">
+        <f>C10*1.1</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="60"/>
+      <c r="H10" s="40" t="s">
+        <v>14</v>
       </c>
       <c r="I10" s="40"/>
-      <c r="J10" s="38"/>
+      <c r="J10" s="55"/>
       <c r="K10" s="38"/>
       <c r="L10" s="1"/>
     </row>
     <row r="11" spans="1:12" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
-      <c r="B11" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="64"/>
-      <c r="D11" s="65"/>
-      <c r="E11" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="64">
-        <f>C11*1.1</f>
-        <v>0</v>
-      </c>
-      <c r="G11" s="65"/>
-      <c r="H11" s="40" t="s">
-        <v>14</v>
-      </c>
-      <c r="I11" s="40"/>
-      <c r="J11" s="52"/>
-      <c r="K11" s="38"/>
+      <c r="B11" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="39"/>
+      <c r="D11" s="58"/>
+      <c r="E11" s="58"/>
+      <c r="F11" s="58"/>
+      <c r="G11" s="55"/>
+      <c r="H11" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" s="5"/>
+      <c r="J11" s="56"/>
+      <c r="K11" s="57"/>
       <c r="L11" s="1"/>
     </row>
-    <row r="12" spans="1:12" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="1"/>
-      <c r="B12" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="39"/>
-      <c r="D12" s="55"/>
-      <c r="E12" s="55"/>
-      <c r="F12" s="55"/>
-      <c r="G12" s="52"/>
-      <c r="H12" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="I12" s="5"/>
-      <c r="J12" s="53"/>
-      <c r="K12" s="54"/>
+      <c r="B12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="8"/>
+      <c r="J12" s="27"/>
+      <c r="K12" s="28"/>
       <c r="L12" s="1"/>
     </row>
     <row r="13" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="1"/>
-      <c r="B13" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="30"/>
+      <c r="B13" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="32"/>
       <c r="H13" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I13" s="8"/>
       <c r="J13" s="27"/>
@@ -1546,107 +1514,109 @@
     <row r="14" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="1"/>
       <c r="B14" s="10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C14" s="31"/>
       <c r="D14" s="31"/>
       <c r="E14" s="31"/>
       <c r="F14" s="31"/>
-      <c r="G14" s="32"/>
+      <c r="G14" s="31"/>
       <c r="H14" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I14" s="8"/>
       <c r="J14" s="27"/>
       <c r="K14" s="28"/>
       <c r="L14" s="1"/>
     </row>
-    <row r="15" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="1"/>
-      <c r="B15" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="I15" s="8"/>
-      <c r="J15" s="27"/>
-      <c r="K15" s="28"/>
+      <c r="B15" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="37"/>
+      <c r="D15" s="37"/>
+      <c r="E15" s="37"/>
+      <c r="F15" s="37"/>
+      <c r="G15" s="37"/>
+      <c r="H15" s="37"/>
+      <c r="I15" s="37"/>
+      <c r="J15" s="37"/>
+      <c r="K15" s="37"/>
       <c r="L15" s="1"/>
     </row>
-    <row r="16" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="1"/>
-      <c r="B16" s="37" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="37"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="37"/>
-      <c r="G16" s="37"/>
-      <c r="H16" s="37"/>
-      <c r="I16" s="37"/>
-      <c r="J16" s="37"/>
-      <c r="K16" s="37"/>
+      <c r="B16" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="F16" s="34"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="J16" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="K16" s="12" t="s">
+        <v>27</v>
+      </c>
       <c r="L16" s="1"/>
     </row>
     <row r="17" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="1"/>
       <c r="B17" s="11" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C17" s="33"/>
       <c r="D17" s="33"/>
       <c r="E17" s="10" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F17" s="34"/>
       <c r="G17" s="35"/>
       <c r="H17" s="36"/>
-      <c r="I17" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="J17" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="K17" s="12" t="s">
-        <v>27</v>
-      </c>
+      <c r="I17" s="13"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="14"/>
       <c r="L17" s="1"/>
     </row>
-    <row r="18" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="1"/>
-      <c r="B18" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" s="33"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="F18" s="34"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="36"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="14"/>
-      <c r="K18" s="14"/>
+      <c r="B18" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="25"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="17"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="17"/>
       <c r="L18" s="1"/>
     </row>
     <row r="19" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="1"/>
       <c r="B19" s="25" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C19" s="25"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
+      <c r="D19" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="E19" s="26"/>
       <c r="F19" s="16" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G19" s="17"/>
       <c r="H19" s="17"/>
@@ -1655,29 +1625,25 @@
       <c r="K19" s="17"/>
       <c r="L19" s="1"/>
     </row>
-    <row r="20" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:12" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="1"/>
-      <c r="B20" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" s="25"/>
-      <c r="D20" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="E20" s="26"/>
-      <c r="F20" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="17"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
       <c r="L20" s="1"/>
     </row>
-    <row r="21" spans="1:12" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:12" ht="18.75" x14ac:dyDescent="0.15">
       <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
+      <c r="B21" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
@@ -1689,116 +1655,116 @@
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
     </row>
-    <row r="22" spans="1:12" ht="18.75" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="1"/>
-      <c r="B22" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
+      <c r="B22" s="61"/>
+      <c r="C22" s="61"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="F22" s="53"/>
+      <c r="G22" s="53"/>
+      <c r="H22" s="53"/>
+      <c r="I22" s="53"/>
+      <c r="J22" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="K22" s="54"/>
       <c r="L22" s="1"/>
     </row>
-    <row r="23" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="1"/>
-      <c r="B23" s="45" t="s">
-        <v>37</v>
-      </c>
-      <c r="C23" s="46"/>
-      <c r="D23" s="46"/>
-      <c r="E23" s="47" t="s">
-        <v>2</v>
-      </c>
-      <c r="F23" s="24"/>
-      <c r="G23" s="24"/>
-      <c r="H23" s="24"/>
-      <c r="I23" s="24"/>
-      <c r="J23" s="19"/>
-      <c r="K23" s="19"/>
+      <c r="B23" s="62"/>
+      <c r="C23" s="62"/>
+      <c r="D23" s="62"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
       <c r="L23" s="1"/>
     </row>
-    <row r="24" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="1"/>
-      <c r="B24" s="45" t="s">
-        <v>38</v>
-      </c>
-      <c r="C24" s="46"/>
-      <c r="D24" s="46"/>
-      <c r="E24" s="47"/>
-      <c r="F24" s="49"/>
-      <c r="G24" s="49"/>
-      <c r="H24" s="49"/>
-      <c r="I24" s="49"/>
-      <c r="J24" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="K24" s="50"/>
+      <c r="B24" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
       <c r="L24" s="1"/>
     </row>
-    <row r="25" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
-      <c r="B25" s="51"/>
-      <c r="C25" s="51"/>
-      <c r="D25" s="51"/>
-      <c r="E25" s="48"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
+      <c r="B25" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="25"/>
+      <c r="J25" s="25"/>
+      <c r="K25" s="25"/>
       <c r="L25" s="1"/>
     </row>
-    <row r="26" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:12" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
-      <c r="B26" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
+      <c r="B26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="38"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="38"/>
+      <c r="G26" s="39"/>
+      <c r="H26" s="40" t="s">
+        <v>6</v>
+      </c>
+      <c r="I26" s="40"/>
+      <c r="J26" s="38"/>
+      <c r="K26" s="38"/>
       <c r="L26" s="1"/>
     </row>
-    <row r="27" spans="1:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
-      <c r="B27" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="C27" s="25"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="25"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="25"/>
-      <c r="H27" s="25"/>
-      <c r="I27" s="25"/>
-      <c r="J27" s="25"/>
-      <c r="K27" s="25"/>
+      <c r="B27" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="47"/>
+      <c r="D27" s="48"/>
+      <c r="E27" s="48"/>
+      <c r="F27" s="48"/>
+      <c r="G27" s="49"/>
+      <c r="H27" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="I27" s="40"/>
+      <c r="J27" s="38"/>
+      <c r="K27" s="38"/>
       <c r="L27" s="1"/>
     </row>
     <row r="28" spans="1:12" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
-      <c r="B28" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C28" s="38"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="39"/>
+      <c r="B28" s="46"/>
+      <c r="C28" s="50"/>
+      <c r="D28" s="51"/>
+      <c r="E28" s="51"/>
+      <c r="F28" s="51"/>
+      <c r="G28" s="52"/>
       <c r="H28" s="40" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I28" s="40"/>
       <c r="J28" s="38"/>
@@ -1807,16 +1773,18 @@
     </row>
     <row r="29" spans="1:12" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
-      <c r="B29" s="56" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="58"/>
-      <c r="D29" s="59"/>
-      <c r="E29" s="59"/>
-      <c r="F29" s="59"/>
-      <c r="G29" s="60"/>
-      <c r="H29" s="40" t="s">
-        <v>8</v>
+      <c r="B29" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C29" s="42"/>
+      <c r="D29" s="42"/>
+      <c r="E29" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F29" s="43"/>
+      <c r="G29" s="44"/>
+      <c r="H29" s="41" t="s">
+        <v>12</v>
       </c>
       <c r="I29" s="40"/>
       <c r="J29" s="38"/>
@@ -1825,313 +1793,273 @@
     </row>
     <row r="30" spans="1:12" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
-      <c r="B30" s="57"/>
-      <c r="C30" s="61"/>
-      <c r="D30" s="62"/>
-      <c r="E30" s="62"/>
-      <c r="F30" s="62"/>
-      <c r="G30" s="63"/>
+      <c r="B30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="59"/>
+      <c r="D30" s="60"/>
+      <c r="E30" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="59">
+        <f>C30*1.1</f>
+        <v>0</v>
+      </c>
+      <c r="G30" s="60"/>
       <c r="H30" s="40" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I30" s="40"/>
-      <c r="J30" s="38"/>
+      <c r="J30" s="55"/>
       <c r="K30" s="38"/>
       <c r="L30" s="1"/>
     </row>
     <row r="31" spans="1:12" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
-      <c r="B31" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="C31" s="42"/>
-      <c r="D31" s="42"/>
-      <c r="E31" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F31" s="43"/>
-      <c r="G31" s="44"/>
-      <c r="H31" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="I31" s="40"/>
-      <c r="J31" s="38"/>
-      <c r="K31" s="38"/>
+      <c r="B31" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="39"/>
+      <c r="D31" s="58"/>
+      <c r="E31" s="58"/>
+      <c r="F31" s="58"/>
+      <c r="G31" s="55"/>
+      <c r="H31" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="I31" s="5"/>
+      <c r="J31" s="56"/>
+      <c r="K31" s="57"/>
       <c r="L31" s="1"/>
     </row>
-    <row r="32" spans="1:12" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="1"/>
-      <c r="B32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="64"/>
-      <c r="D32" s="65"/>
-      <c r="E32" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="F32" s="64">
-        <f>C32*1.1</f>
-        <v>0</v>
-      </c>
-      <c r="G32" s="65"/>
-      <c r="H32" s="40" t="s">
-        <v>14</v>
-      </c>
-      <c r="I32" s="40"/>
-      <c r="J32" s="52"/>
-      <c r="K32" s="38"/>
+      <c r="B32" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I32" s="8"/>
+      <c r="J32" s="27"/>
+      <c r="K32" s="28"/>
       <c r="L32" s="1"/>
     </row>
-    <row r="33" spans="1:12" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="1"/>
-      <c r="B33" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="C33" s="39"/>
-      <c r="D33" s="55"/>
-      <c r="E33" s="55"/>
-      <c r="F33" s="55"/>
-      <c r="G33" s="52"/>
-      <c r="H33" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="I33" s="5"/>
-      <c r="J33" s="53"/>
-      <c r="K33" s="54"/>
+      <c r="B33" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I33" s="8"/>
+      <c r="J33" s="27"/>
+      <c r="K33" s="28"/>
       <c r="L33" s="1"/>
     </row>
     <row r="34" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="1"/>
-      <c r="B34" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" s="29"/>
-      <c r="D34" s="29"/>
-      <c r="E34" s="29"/>
-      <c r="F34" s="29"/>
-      <c r="G34" s="30"/>
+      <c r="B34" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" s="31"/>
+      <c r="D34" s="31"/>
+      <c r="E34" s="31"/>
+      <c r="F34" s="31"/>
+      <c r="G34" s="31"/>
       <c r="H34" s="7" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I34" s="8"/>
       <c r="J34" s="27"/>
       <c r="K34" s="28"/>
       <c r="L34" s="1"/>
     </row>
-    <row r="35" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="1"/>
-      <c r="B35" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="32"/>
-      <c r="H35" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I35" s="8"/>
-      <c r="J35" s="27"/>
-      <c r="K35" s="28"/>
+      <c r="B35" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="C35" s="37"/>
+      <c r="D35" s="37"/>
+      <c r="E35" s="37"/>
+      <c r="F35" s="37"/>
+      <c r="G35" s="37"/>
+      <c r="H35" s="37"/>
+      <c r="I35" s="37"/>
+      <c r="J35" s="37"/>
+      <c r="K35" s="37"/>
       <c r="L35" s="1"/>
     </row>
     <row r="36" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="1"/>
-      <c r="B36" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C36" s="31"/>
-      <c r="D36" s="31"/>
-      <c r="E36" s="31"/>
-      <c r="F36" s="31"/>
-      <c r="G36" s="31"/>
-      <c r="H36" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="I36" s="8"/>
-      <c r="J36" s="27"/>
-      <c r="K36" s="28"/>
+      <c r="B36" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C36" s="33"/>
+      <c r="D36" s="33"/>
+      <c r="E36" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="F36" s="34"/>
+      <c r="G36" s="35"/>
+      <c r="H36" s="36"/>
+      <c r="I36" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="J36" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="K36" s="12" t="s">
+        <v>27</v>
+      </c>
       <c r="L36" s="1"/>
     </row>
-    <row r="37" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="1"/>
-      <c r="B37" s="37" t="s">
-        <v>22</v>
-      </c>
-      <c r="C37" s="37"/>
-      <c r="D37" s="37"/>
-      <c r="E37" s="37"/>
-      <c r="F37" s="37"/>
-      <c r="G37" s="37"/>
-      <c r="H37" s="37"/>
-      <c r="I37" s="37"/>
-      <c r="J37" s="37"/>
-      <c r="K37" s="37"/>
+      <c r="B37" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C37" s="33"/>
+      <c r="D37" s="33"/>
+      <c r="E37" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F37" s="34"/>
+      <c r="G37" s="35"/>
+      <c r="H37" s="36"/>
+      <c r="I37" s="13"/>
+      <c r="J37" s="14"/>
+      <c r="K37" s="14"/>
       <c r="L37" s="1"/>
     </row>
-    <row r="38" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="1"/>
-      <c r="B38" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C38" s="33"/>
-      <c r="D38" s="33"/>
-      <c r="E38" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="F38" s="34"/>
-      <c r="G38" s="35"/>
-      <c r="H38" s="36"/>
-      <c r="I38" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="J38" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="K38" s="12" t="s">
-        <v>27</v>
-      </c>
+      <c r="B38" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C38" s="25"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="G38" s="17"/>
+      <c r="H38" s="17"/>
+      <c r="I38" s="17"/>
+      <c r="J38" s="17"/>
+      <c r="K38" s="17"/>
       <c r="L38" s="1"/>
     </row>
-    <row r="39" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="1"/>
-      <c r="B39" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C39" s="33"/>
-      <c r="D39" s="33"/>
-      <c r="E39" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="F39" s="34"/>
-      <c r="G39" s="35"/>
-      <c r="H39" s="36"/>
-      <c r="I39" s="13"/>
-      <c r="J39" s="14"/>
-      <c r="K39" s="14"/>
+      <c r="B39" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C39" s="25"/>
+      <c r="D39" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="E39" s="26"/>
+      <c r="F39" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="G39" s="17"/>
+      <c r="H39" s="17"/>
+      <c r="I39" s="17"/>
+      <c r="J39" s="17"/>
+      <c r="K39" s="17"/>
       <c r="L39" s="1"/>
     </row>
-    <row r="40" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="1"/>
-      <c r="B40" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="C40" s="25"/>
-      <c r="D40" s="15"/>
-      <c r="E40" s="15"/>
-      <c r="F40" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="G40" s="17"/>
-      <c r="H40" s="17"/>
-      <c r="I40" s="17"/>
-      <c r="J40" s="17"/>
-      <c r="K40" s="17"/>
-      <c r="L40" s="1"/>
-    </row>
-    <row r="41" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="1"/>
-      <c r="B41" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="C41" s="25"/>
-      <c r="D41" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="E41" s="26"/>
-      <c r="F41" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="G41" s="17"/>
-      <c r="H41" s="17"/>
-      <c r="I41" s="17"/>
-      <c r="J41" s="17"/>
-      <c r="K41" s="17"/>
-      <c r="L41" s="1"/>
-    </row>
   </sheetData>
-  <mergeCells count="80">
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="F3:I3"/>
-    <mergeCell ref="B6:K6"/>
-    <mergeCell ref="C7:G7"/>
+  <mergeCells count="76">
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:G8"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="B5:K5"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="J2:K2"/>
     <mergeCell ref="H7:I7"/>
     <mergeCell ref="J7:K7"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="J3:K3"/>
     <mergeCell ref="H8:I8"/>
     <mergeCell ref="J8:K8"/>
+    <mergeCell ref="C9:D9"/>
     <mergeCell ref="H9:I9"/>
     <mergeCell ref="J9:K9"/>
-    <mergeCell ref="C10:D10"/>
     <mergeCell ref="H10:I10"/>
     <mergeCell ref="J10:K10"/>
-    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="F9:G9"/>
     <mergeCell ref="J11:K11"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="C11:G11"/>
     <mergeCell ref="C12:G12"/>
     <mergeCell ref="C13:G13"/>
     <mergeCell ref="C14:G14"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="B16:K16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="B15:K15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="J12:K12"/>
     <mergeCell ref="J13:K13"/>
     <mergeCell ref="J14:K14"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B18:C18"/>
     <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:E25"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="F24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B27:K27"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C27:G28"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="B35:K35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="B22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="B25:K25"/>
+    <mergeCell ref="C26:G26"/>
     <mergeCell ref="H28:I28"/>
     <mergeCell ref="J28:K28"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:G30"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="B37:K37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="H26:I26"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.39370078740157483" right="0" top="0.35" bottom="0" header="0" footer="0"/>
